--- a/artfynd/A 23893-2023 artfynd.xlsx
+++ b/artfynd/A 23893-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>121086742</v>
       </c>
       <c r="B3" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 23893-2023 artfynd.xlsx
+++ b/artfynd/A 23893-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>121086742</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 23893-2023 artfynd.xlsx
+++ b/artfynd/A 23893-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>121086742</v>
       </c>
       <c r="B3" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 23893-2023 artfynd.xlsx
+++ b/artfynd/A 23893-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>120738161</v>
       </c>
       <c r="B2" t="n">
-        <v>98059</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,12 +794,7 @@
         <v>121086742</v>
       </c>
       <c r="B3" t="n">
-        <v>98095</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
